--- a/セリフ編集/ナレーション・記事/実況・演出.xlsx
+++ b/セリフ編集/ナレーション・記事/実況・演出.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -715,223 +715,223 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR.high[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high[1]</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">歴史に残る名勝負</t>
+          <t xml:space="preserve">二人の連打が止まらない！ これがタッグの醍醐味！</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR.high[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high[2]</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">会場が震えた一戦</t>
+          <t xml:space="preserve">連携の打撃ラッシュ！ 息がぴったり合っている！</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR.high[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[3]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high[3]</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すべてを出し尽くした激闘</t>
+          <t xml:space="preserve">挟み撃ちの打撃コンビネーション！ 逃げ場がない！</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR.mid[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[4]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mid[1]</t>
+          <t xml:space="preserve">[4]</t>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">観客を沸かせた好勝負</t>
+          <t xml:space="preserve">左右から浴びせる打撃！ 二人の攻撃が完全にシンクロしている！</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR.mid[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[5]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mid[2]</t>
+          <t xml:space="preserve">[5]</t>
         </is>
       </c>
       <c r="G23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">互いの意地がぶつかり合った一戦</t>
+          <t xml:space="preserve">ダブル打撃の嵐！ 相手は防ぎきれない！</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR.mid[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[6]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR</t>
+          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mid[3]</t>
+          <t xml:space="preserve">[6]</t>
         </is>
       </c>
       <c r="G24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">技と力が交錯する見応えある試合</t>
+          <t xml:space="preserve">コンビの拳とキックが次々に突き刺さる！</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR.low[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">low[1]</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">光るものを見せた一戦</t>
+          <t xml:space="preserve">息の合ったダブルスロー！ これぞタッグの真骨頂！</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR.low[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BESTMATCH_FLAVOR</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">low[2]</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">荒削りだが熱い闘い</t>
+          <t xml:space="preserve">二人がかりの豪快な投げ技！ 会場が揺れる！</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[3]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -941,24 +941,24 @@
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人の連打が止まらない！ これがタッグの醍醐味！</t>
+          <t xml:space="preserve">連係の投げ技が完璧に決まった！</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[4]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -968,24 +968,24 @@
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">[4]</t>
         </is>
       </c>
       <c r="G28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連携の打撃ラッシュ！ 息がぴったり合っている！</t>
+          <t xml:space="preserve">受け渡し式の投げ技！ 相手は空中で何も出来ない！</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[5]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -995,24 +995,24 @@
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">[5]</t>
         </is>
       </c>
       <c r="G29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挟み撃ちの打撃コンビネーション！ 逃げ場がない！</t>
+          <t xml:space="preserve">ダブルパワーで投げ切った！ まるで振り子のようだ！</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[4]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[6]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4]</t>
+          <t xml:space="preserve">[6]</t>
         </is>
       </c>
       <c r="G30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">左右から浴びせる打撃！ 二人の攻撃が完全にシンクロしている！</t>
+          <t xml:space="preserve">二人の呼吸が合った一瞬の投げ！ 決まった！</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[5]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5]</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ダブル打撃の嵐！ 相手は防ぎきれない！</t>
+          <t xml:space="preserve">二人がかりの極め技！ もう動けない！</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES[6]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[6]</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コンビの拳とキックが次々に突き刺さる！</t>
+          <t xml:space="preserve">上下から襲いかかる関節技！ これは危険だ！</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[3]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">息の合ったダブルスロー！ これぞタッグの真骨頂！</t>
+          <t xml:space="preserve">セットアップから一気に極めた！ 逃げ場がない！</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[4]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">[4]</t>
         </is>
       </c>
       <c r="G34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人がかりの豪快な投げ技！ 会場が揺れる！</t>
+          <t xml:space="preserve">ダブルロック！ 二人分の力で関節を締め上げる！</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[5]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">[5]</t>
         </is>
       </c>
       <c r="G35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連係の投げ技が完璧に決まった！</t>
+          <t xml:space="preserve">連係の関節技！ 相手は苦悶の表情を浮かべる！</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[4]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[6]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4]</t>
+          <t xml:space="preserve">[6]</t>
         </is>
       </c>
       <c r="G36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受け渡し式の投げ技！ 相手は空中で何も出来ない！</t>
+          <t xml:space="preserve">二人で極めにいった！ これは返せない！</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[5]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5]</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ダブルパワーで投げ切った！ まるで振り子のようだ！</t>
+          <t xml:space="preserve">空中から二重の衝撃！ 圧巻のダブルフライ！</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES[6]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1238,24 +1238,24 @@
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[6]</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人の呼吸が合った一瞬の投げ！ 決まった！</t>
+          <t xml:space="preserve">タワー式のダイビング技！ 会場が沸いている！</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人がかりの極め技！ もう動けない！</t>
+          <t xml:space="preserve">シンクロ空中技が炸裂！ これは止められない！</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[4]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">[4]</t>
         </is>
       </c>
       <c r="G40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上下から襲いかかる関節技！ これは危険だ！</t>
+          <t xml:space="preserve">コンビの飛び技が連続で突き刺さる！</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[5]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">[5]</t>
         </is>
       </c>
       <c r="G41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">セットアップから一気に極めた！ 逃げ場がない！</t>
+          <t xml:space="preserve">空中戦の完璧な連携！ 二人のタイミングは完全一致！</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[4]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[6]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4]</t>
+          <t xml:space="preserve">[6]</t>
         </is>
       </c>
       <c r="G42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ダブルロック！ 二人分の力で関節を締め上げる！</t>
+          <t xml:space="preserve">一人が踏み台、もう一人が飛ぶ！ タッグでしか出来ない技！</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[5]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5]</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連係の関節技！ 相手は苦悶の表情を浮かべる！</t>
+          <t xml:space="preserve">これは決まった！ タッグの絆が生んだ一撃！</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES[6]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES[2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[6]</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人で極めにいった！ これは返せない！</t>
+          <t xml:space="preserve">フィニッシュだ！ 二人の信頼が織りなす必殺技！</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES[3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">空中から二重の衝撃！ 圧巻のダブルフライ！</t>
+          <t xml:space="preserve">息の合った一撃で仕留めた！ これがタッグの勝利！</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES[4]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">[4]</t>
         </is>
       </c>
       <c r="G46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タワー式のダイビング技！ 会場が沸いている！</t>
+          <t xml:space="preserve">完璧なダブルチームで決着！ 二人の強さが証明された！</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES[5]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
+          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">[5]</t>
         </is>
       </c>
       <c r="G47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">シンクロ空中技が炸裂！ これは止められない！</t>
+          <t xml:space="preserve">連係の果ての必殺技！ 相手は立てない！</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[4]</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4]</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コンビの飛び技が連続で突き刺さる！</t>
+          <t xml:space="preserve">{winner}組、見事なコンビネーションで勝利を掴んだ！</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[5]</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[2]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5]</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">空中戦の完璧な連携！ 二人のタイミングは完全一致！</t>
+          <t xml:space="preserve">息の合ったタッグワークが勝負を決めた！ {winner}&amp;{partner}、完勝！</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES[6]</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[3]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[6]</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人が踏み台、もう一人が飛ぶ！ タッグでしか出来ない技！</t>
+          <t xml:space="preserve">これがタッグの強さだ！ {winner}組、見事な勝利！</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES[1]</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[4]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">[4]</t>
         </is>
       </c>
       <c r="G51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これは決まった！ タッグの絆が生んだ一撃！</t>
+          <t xml:space="preserve">{winner}と{partner}の信頼が生んだ一撃！ 歴史に残る名勝負だ！</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES[2]</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[5]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">[5]</t>
         </is>
       </c>
       <c r="G52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フィニッシュだ！ 二人の信頼が織りなす必殺技！</t>
+          <t xml:space="preserve">タッグの醍醐味を見せつけた！ {winner}組、堂々の勝利！</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES[3]</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[6]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">[6]</t>
         </is>
       </c>
       <c r="G53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">息の合った一撃で仕留めた！ これがタッグの勝利！</t>
+          <t xml:space="preserve">二人の絆が勝敗を分けた！ {winner}組の勝利！</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES[4]</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[7]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1670,240 +1670,240 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4]</t>
+          <t xml:space="preserve">[7]</t>
         </is>
       </c>
       <c r="G54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完璧なダブルチームで決着！ 二人の強さが証明された！</t>
+          <t xml:space="preserve">{move}で決着！ {winner}&amp;{partner}のコンビが頂点に立った！</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES[5]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.bestFriends[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5]</t>
+          <t xml:space="preserve">bestFriends[1]</t>
         </is>
       </c>
       <c r="G55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連係の果ての必殺技！ 相手は立てない！</t>
+          <t xml:space="preserve">{nameA}と{nameB}が練習後に並んで帰る姿が目撃された</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.bestFriends[2]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">bestFriends[2]</t>
         </is>
       </c>
       <c r="G56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{winner}組、見事なコンビネーションで勝利を掴んだ！</t>
+          <t xml:space="preserve">{nameA}と{nameB}がトレーニングで息の合った動きを見せている</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.bestFriends[3]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">bestFriends[3]</t>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">息の合ったタッグワークが勝負を決めた！ {winner}&amp;{partner}、完勝！</t>
+          <t xml:space="preserve">{nameA}が{nameB}の体調を気遣っている姿があった</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.hostileEnemy[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">hostileEnemy[1]</t>
         </is>
       </c>
       <c r="G58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これがタッグの強さだ！ {winner}組、見事な勝利！</t>
+          <t xml:space="preserve">{nameA}と{nameB}の間に張り詰めた空気が漂っている</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[4]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.hostileEnemy[2]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4]</t>
+          <t xml:space="preserve">hostileEnemy[2]</t>
         </is>
       </c>
       <c r="G59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{winner}と{partner}の信頼が生んだ一撃！ 歴史に残る名勝負だ！</t>
+          <t xml:space="preserve">{nameA}と{nameB}が控室で目も合わせない</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[5]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.hostileEnemy[3]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5]</t>
+          <t xml:space="preserve">hostileEnemy[3]</t>
         </is>
       </c>
       <c r="G60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タッグの醍醐味を見せつけた！ {winner}組、堂々の勝利！</t>
+          <t xml:space="preserve">ロッカールームの一角で{nameA}と{nameB}の冷たい空気が流れている</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[6]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.clash[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[6]</t>
+          <t xml:space="preserve">clash[1]</t>
         </is>
       </c>
       <c r="G61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人の絆が勝敗を分けた！ {winner}組の勝利！</t>
+          <t xml:space="preserve">{nameA}と{nameB}が練習中に激しく言い合いになった</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES[7]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.clash[2]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[7]</t>
+          <t xml:space="preserve">clash[2]</t>
         </is>
       </c>
       <c r="G62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{move}で決着！ {winner}&amp;{partner}のコンビが頂点に立った！</t>
+          <t xml:space="preserve">{nameA}と{nameB}の口論が控室に響いた</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.bestFriends[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.clash[3]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestFriends[1]</t>
+          <t xml:space="preserve">clash[3]</t>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}が練習後に並んで帰る姿が目撃された</t>
+          <t xml:space="preserve">{nameA}が{nameB}に食ってかかり、スタッフが止めに入った</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.bestFriends[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.clash[4]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestFriends[2]</t>
+          <t xml:space="preserve">clash[4]</t>
         </is>
       </c>
       <c r="G64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}がトレーニングで息の合った動きを見せている</t>
+          <t xml:space="preserve">{nameA}と{nameB}の間で一触即発の空気が走った</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.bestFriends[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.clash[5]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestFriends[3]</t>
+          <t xml:space="preserve">clash[5]</t>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}が{nameB}の体調を気遣っている姿があった</t>
+          <t xml:space="preserve">{nameA}と{nameB}が掴み合いになりかけ、周囲が慌てて止めた</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.hostileEnemy[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalZone[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostileEnemy[1]</t>
+          <t xml:space="preserve">goodRivalZone[1]</t>
         </is>
       </c>
       <c r="G66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}の間に張り詰めた空気が漂っている</t>
+          <t xml:space="preserve">{nameA}が{nameB}の試合映像を繰り返し見ている</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.hostileEnemy[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalZone[2]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostileEnemy[2]</t>
+          <t xml:space="preserve">goodRivalZone[2]</t>
         </is>
       </c>
       <c r="G67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}が控室で目も合わせない</t>
+          <t xml:space="preserve">{nameA}と{nameB}が練習後に言葉を交わし、互いに頷いていた</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.hostileEnemy[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalZone[3]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hostileEnemy[3]</t>
+          <t xml:space="preserve">goodRivalZone[3]</t>
         </is>
       </c>
       <c r="G68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ロッカールームの一角で{nameA}と{nameB}の冷たい空気が流れている</t>
+          <t xml:space="preserve">{nameA}は{nameB}の試合結果を真っ先に確認している</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.clash[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.unrequitedBond[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">clash[1]</t>
+          <t xml:space="preserve">unrequitedBond[1]</t>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}が練習中に激しく言い合いになった</t>
+          <t xml:space="preserve">{nameA}が{nameB}に話しかけるも、素っ気ない反応だった</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.clash[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.unrequitedBond[2]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">clash[2]</t>
+          <t xml:space="preserve">unrequitedBond[2]</t>
         </is>
       </c>
       <c r="G70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}の口論が控室に響いた</t>
+          <t xml:space="preserve">{nameA}は{nameB}のことを親友だと思っている——{nameB}がどう思っているかは別として</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.clash[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.unrequitedBond[3]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">clash[3]</t>
+          <t xml:space="preserve">unrequitedBond[3]</t>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}が{nameB}に食ってかかり、スタッフが止めに入った</t>
+          <t xml:space="preserve">{nameA}が{nameB}を誘うが、{nameB}は別の用事があると去っていった</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.clash[4]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.onesidedHostility[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">clash[4]</t>
+          <t xml:space="preserve">onesidedHostility[1]</t>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}の間で一触即発の空気が走った</t>
+          <t xml:space="preserve">{nameA}が{nameB}を睨みつけている。{nameB}は気づいていない</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.clash[5]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.onesidedHostility[2]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">clash[5]</t>
+          <t xml:space="preserve">onesidedHostility[2]</t>
         </is>
       </c>
       <c r="G73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}が掴み合いになりかけ、周囲が慌てて止めた</t>
+          <t xml:space="preserve">{nameA}は{nameB}の名前を聞くたびに表情を歪めている</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalZone[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.onesidedHostility[3]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodRivalZone[1]</t>
+          <t xml:space="preserve">onesidedHostility[3]</t>
         </is>
       </c>
       <c r="G74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}が{nameB}の試合映像を繰り返し見ている</t>
+          <t xml:space="preserve">{nameA}の練習が日に日に荒くなっている——{nameB}への執念が滲む</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalZone[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.temperatureDiff[1]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodRivalZone[2]</t>
+          <t xml:space="preserve">temperatureDiff[1]</t>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}が練習後に言葉を交わし、互いに頷いていた</t>
+          <t xml:space="preserve">{nameA}が{nameB}との距離に少し戸惑っている様子だ</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalZone[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.temperatureDiff[2]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodRivalZone[3]</t>
+          <t xml:space="preserve">temperatureDiff[2]</t>
         </is>
       </c>
       <c r="G76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}は{nameB}の試合結果を真っ先に確認している</t>
+          <t xml:space="preserve">{nameA}は{nameB}との関係をもっと深めたいようだが……</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.unrequitedBond[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.crossAsymmetry[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">unrequitedBond[1]</t>
+          <t xml:space="preserve">crossAsymmetry[1]</t>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}が{nameB}に話しかけるも、素っ気ない反応だった</t>
+          <t xml:space="preserve">{nameA}は{nameB}を目の敵にしている。{nameB}は{nameA}のことを仲間だと思っているのに</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.unrequitedBond[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.crossAsymmetry[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">unrequitedBond[2]</t>
+          <t xml:space="preserve">crossAsymmetry[2]</t>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}は{nameB}のことを親友だと思っている——{nameB}がどう思っているかは別として</t>
+          <t xml:space="preserve">{nameB}が笑顔で話しかけた{nameA}は、拳を握りしめて背を向けた</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.unrequitedBond[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.highRivalryAwareness[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">unrequitedBond[3]</t>
+          <t xml:space="preserve">highRivalryAwareness[1]</t>
         </is>
       </c>
       <c r="G79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}が{nameB}を誘うが、{nameB}は別の用事があると去っていった</t>
+          <t xml:space="preserve">{nameA}は客席から{nameB}の試合を食い入るように見つめていた</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.onesidedHostility[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.highRivalryAwareness[2]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">onesidedHostility[1]</t>
+          <t xml:space="preserve">highRivalryAwareness[2]</t>
         </is>
       </c>
       <c r="G80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}が{nameB}を睨みつけている。{nameB}は気づいていない</t>
+          <t xml:space="preserve">{nameA}は{nameB}の試合結果を聞いて、ゆっくりとテーピングを巻き直した</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.onesidedHostility[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.highRivalryAwareness[3]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">onesidedHostility[2]</t>
+          <t xml:space="preserve">highRivalryAwareness[3]</t>
         </is>
       </c>
       <c r="G81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}は{nameB}の名前を聞くたびに表情を歪めている</t>
+          <t xml:space="preserve">{nameA}が{nameB}の勝利を知り、静かに拳を握った</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.onesidedHostility[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.highRivalryAwareness[4]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">onesidedHostility[3]</t>
+          <t xml:space="preserve">highRivalryAwareness[4]</t>
         </is>
       </c>
       <c r="G82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}の練習が日に日に荒くなっている——{nameB}への執念が滲む</t>
+          <t xml:space="preserve">花道の奥から{nameA}が{nameB}の試合を見ていた。その目は揺れていない</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.temperatureDiff[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalTicker[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">temperatureDiff[1]</t>
+          <t xml:space="preserve">goodRivalTicker[1]</t>
         </is>
       </c>
       <c r="G83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}が{nameB}との距離に少し戸惑っている様子だ</t>
+          <t xml:space="preserve">{nameA}と{nameB}が練習後に静かに言葉を交わしていた</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.temperatureDiff[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalTicker[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">temperatureDiff[2]</t>
+          <t xml:space="preserve">goodRivalTicker[2]</t>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}は{nameB}との関係をもっと深めたいようだが……</t>
+          <t xml:space="preserve">{nameA}と{nameB}——好敵手の二人が並んでストレッチをしている</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.crossAsymmetry[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalTicker[3]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">crossAsymmetry[1]</t>
+          <t xml:space="preserve">goodRivalTicker[3]</t>
         </is>
       </c>
       <c r="G85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}は{nameB}を目の敵にしている。{nameB}は{nameA}のことを仲間だと思っているのに</t>
+          <t xml:space="preserve">{nameA}は{nameB}の試合を見て、小さく微笑んだ</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.crossAsymmetry[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.bitterRivalTicker[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">crossAsymmetry[2]</t>
+          <t xml:space="preserve">bitterRivalTicker[1]</t>
         </is>
       </c>
       <c r="G86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が笑顔で話しかけた{nameA}は、拳を握りしめて背を向けた</t>
+          <t xml:space="preserve">{nameA}と{nameB}が控室ですれ違い、空気が凍りついた</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.highRivalryAwareness[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.bitterRivalTicker[2]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">highRivalryAwareness[1]</t>
+          <t xml:space="preserve">bitterRivalTicker[2]</t>
         </is>
       </c>
       <c r="G87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}は客席から{nameB}の試合を食い入るように見つめていた</t>
+          <t xml:space="preserve">{nameA}の表情が一瞬歪んだ——{nameB}の名前を聞いただけで</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.highRivalryAwareness[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.bitterRivalTicker[3]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">highRivalryAwareness[2]</t>
+          <t xml:space="preserve">bitterRivalTicker[3]</t>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}は{nameB}の試合結果を聞いて、ゆっくりとテーピングを巻き直した</t>
+          <t xml:space="preserve">{nameA}と{nameB}が同じ廊下を歩くことを、誰もが避けさせている</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.highRivalryAwareness[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.trustWarning[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">highRivalryAwareness[3]</t>
+          <t xml:space="preserve">trustWarning[1]</t>
         </is>
       </c>
       <c r="G89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}が{nameB}の勝利を知り、静かに拳を握った</t>
+          <t xml:space="preserve">{name}の表情が最近曇っている</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.highRivalryAwareness[4]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.trustWarning[2]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">highRivalryAwareness[4]</t>
+          <t xml:space="preserve">trustWarning[2]</t>
         </is>
       </c>
       <c r="G90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">花道の奥から{nameA}が{nameB}の試合を見ていた。その目は揺れていない</t>
+          <t xml:space="preserve">{name}の練習への集中力が落ちてきている</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalTicker[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.trustWarning[3]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodRivalTicker[1]</t>
+          <t xml:space="preserve">trustWarning[3]</t>
         </is>
       </c>
       <c r="G91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}が練習後に静かに言葉を交わしていた</t>
+          <t xml:space="preserve">{name}がひとりでロッカールームに佇んでいた</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalTicker[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.trustWarning[4]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodRivalTicker[2]</t>
+          <t xml:space="preserve">trustWarning[4]</t>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}——好敵手の二人が並んでストレッチをしている</t>
+          <t xml:space="preserve">{name}の笑顔が減った——周囲もそれに気づいている</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.goodRivalTicker[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal._default[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -2728,19 +2728,24 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodRivalTicker[3]</t>
+          <t xml:space="preserve">awakening.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}は{nameB}の試合を見て、小さく微笑んだ</t>
+          <t xml:space="preserve">{nameB}が{nameA}に向かって叫んだ。「もう我慢の限界よ！ あなたがそうなら、私も本気で行く！」</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.bitterRivalTicker[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal._default[2]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -2755,19 +2760,24 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterRivalTicker[1]</t>
+          <t xml:space="preserve">awakening.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}が控室ですれ違い、空気が凍りついた</t>
+          <t xml:space="preserve">{nameB}の目の色が変わった。「……もういい。あなたがそう思うなら、私も覚悟を決める」</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.bitterRivalTicker[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold._default[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -2782,19 +2792,24 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterRivalTicker[2]</t>
+          <t xml:space="preserve">awakening.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}の表情が一瞬歪んだ——{nameB}の名前を聞いただけで</t>
+          <t xml:space="preserve">{nameB}が{nameA}の前に立ちはだかった。「いい加減にして。そのつもりなら、全力で相手になるから」</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.bitterRivalTicker[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold._default[2]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -2809,19 +2824,24 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterRivalTicker[3]</t>
+          <t xml:space="preserve">awakening.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameA}と{nameB}が同じ廊下を歩くことを、誰もが避けさせている</t>
+          <t xml:space="preserve">{nameB}が{nameA}をまっすぐ見据えた。「もう黙ってられない。受けて立つよ」</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.trustWarning[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.quiet._default[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -2836,19 +2856,24 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trustWarning[1]</t>
+          <t xml:space="preserve">awakening.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
         </is>
       </c>
       <c r="G97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の表情が最近曇っている</t>
+          <t xml:space="preserve">{nameB}が静かに拳を握った。「ずっと信じてた。でももう……終わりにする」</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.trustWarning[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.shy._default[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -2863,19 +2888,24 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trustWarning[2]</t>
+          <t xml:space="preserve">awakening.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の練習への集中力が落ちてきている</t>
+          <t xml:space="preserve">「…ずっと我慢してた…けど…もう限界です…」——{nameB}の声は小さいけど、震えていなかった</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.trustWarning[3]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.shy._default[2]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -2890,19 +2920,24 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trustWarning[3]</t>
+          <t xml:space="preserve">awakening.shy._default[2]</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}がひとりでロッカールームに佇んでいた</t>
+          <t xml:space="preserve">{nameB}が俯いたまま{nameA}に告げた。「…もう…我慢しない…です」</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.trustWarning[4]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.easygoing._default[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -2917,19 +2952,24 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trustWarning[4]</t>
+          <t xml:space="preserve">awakening.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の笑顔が減った——周囲もそれに気づいている</t>
+          <t xml:space="preserve">{nameB}の笑顔が消えた。「……さすがにさ。これはないよ。本気で怒ってるんだからね」</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal._default[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.earnest._default[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -2944,24 +2984,24 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.normal._default[1]</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">awakening.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が{nameA}に向かって叫んだ。「もう我慢の限界よ！ あなたがそうなら、私も本気で行く！」</t>
+          <t xml:space="preserve">{nameB}が真っ直ぐ{nameA}を見つめた。「ずっと信じていました。でも……もう限界です。本気で行きます」</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.normal._default[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.emotional._default[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -2976,24 +3016,24 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.normal._default[2]</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">awakening.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}の目の色が変わった。「……もういい。あなたがそう思うなら、私も覚悟を決める」</t>
+          <t xml:space="preserve">{nameB}が涙を流しながら{nameA}に叫んだ。「なんで……！ なんでそんなことするの……！ もう……もう許さない……！」</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold._default[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.rivalry[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3003,29 +3043,24 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.bold._default[1]</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">rivalry[1]</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が{nameA}の前に立ちはだかった。「いい加減にして。そのつもりなら、全力で相手になるから」</t>
+          <t xml:space="preserve">因縁の対決！{name1}と{name2}、この大舞台で決着なるか！</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold._default[2]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.rivalry[2]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3035,29 +3070,24 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.bold._default[2]</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">rivalry[2]</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が{nameA}をまっすぐ見据えた。「もう黙ってられない。受けて立つよ」</t>
+          <t xml:space="preserve">積み重ねてきた因縁——{name1}と{name2}の物語が、ここで動く！</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.quiet._default[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.tierGap[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3067,29 +3097,24 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.quiet._default[1]</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">tierGap[1]</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が静かに拳を握った。「ずっと信じてた。でももう……終わりにする」</t>
+          <t xml:space="preserve">{org2}の壁！{name1}は{name2}を越えられるか！</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.shy._default[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.tierGap[2]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3099,29 +3124,24 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.shy._default[1]</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">tierGap[2]</t>
         </is>
       </c>
       <c r="G106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「…ずっと我慢してた…けど…もう限界です…」——{nameB}の声は小さいけど、震えていなかった</t>
+          <t xml:space="preserve">格上挑戦！{name1}が{org2}の{name2}に挑む！</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.shy._default[2]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.closeOVR[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3131,29 +3151,24 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.shy._default[2]</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">closeOVR[1]</t>
         </is>
       </c>
       <c r="G107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が俯いたまま{nameA}に告げた。「…もう…我慢しない…です」</t>
+          <t xml:space="preserve">実力伯仲！{name1}と{name2}、どちらが勝ってもおかしくない！</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.easygoing._default[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.closeOVR[2]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3163,29 +3178,24 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.easygoing._default[1]</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">closeOVR[2]</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}の笑顔が消えた。「……さすがにさ。これはないよ。本気で怒ってるんだからね」</t>
+          <t xml:space="preserve">互角の実力——勝敗を分けるのは、この一瞬の判断！</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.earnest._default[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.starMatch[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3195,29 +3205,24 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.earnest._default[1]</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">starMatch[1]</t>
         </is>
       </c>
       <c r="G109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が真っ直ぐ{nameA}を見つめた。「ずっと信じていました。でも……もう限界です。本気で行きます」</t>
+          <t xml:space="preserve">スター対決！{name1}と{name2}、夢のカードが実現！</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.emotional._default[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.starMatch[2]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3227,29 +3232,24 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.emotional._default[1]</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">starMatch[2]</t>
         </is>
       </c>
       <c r="G110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が涙を流しながら{nameA}に叫んだ。「なんで……！ なんでそんなことするの……！ もう……もう許さない……！」</t>
+          <t xml:space="preserve">人気者同士の激突！{name1} vs {name2}、会場が沸く！</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.rivalry[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.summit[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3264,19 +3264,19 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry[1]</t>
+          <t xml:space="preserve">summit[1]</t>
         </is>
       </c>
       <c r="G111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">因縁の対決！{name1}と{name2}、この大舞台で決着なるか！</t>
+          <t xml:space="preserve">団体の威信を懸けた頂上決戦！{name1} vs {name2}！</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.rivalry[2]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.summit[2]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3291,233 +3291,17 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry[2]</t>
+          <t xml:space="preserve">summit[2]</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">積み重ねてきた因縁——{name1}と{name2}の物語が、ここで動く！</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="40" customHeight="1">
-      <c r="A113" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.tierGap[1]</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">tierGap[1]</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{org2}の壁！{name1}は{name2}を越えられるか！</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="40" customHeight="1">
-      <c r="A114" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.tierGap[2]</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">tierGap[2]</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">格上挑戦！{name1}が{org2}の{name2}に挑む！</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="40" customHeight="1">
-      <c r="A115" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.closeOVR[1]</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">closeOVR[1]</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">実力伯仲！{name1}と{name2}、どちらが勝ってもおかしくない！</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="40" customHeight="1">
-      <c r="A116" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.closeOVR[2]</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">closeOVR[2]</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">互角の実力——勝敗を分けるのは、この一瞬の判断！</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="40" customHeight="1">
-      <c r="A117" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.starMatch[1]</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">starMatch[1]</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">スター対決！{name1}と{name2}、夢のカードが実現！</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="40" customHeight="1">
-      <c r="A118" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.starMatch[2]</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">starMatch[2]</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">人気者同士の激突！{name1} vs {name2}、会場が沸く！</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="40" customHeight="1">
-      <c r="A119" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.summit[1]</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">summit[1]</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">団体の威信を懸けた頂上決戦！{name1} vs {name2}！</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="40" customHeight="1">
-      <c r="A120" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.summit[2]</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">summit[2]</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">年間王者を決める最終決戦——{name1}と{name2}、頂点に立つのはどちらだ！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I120"/>
+  <autoFilter ref="A1:I112"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/ナレーション・記事/実況・演出.xlsx
+++ b/セリフ編集/ナレーション・記事/実況・演出.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2713,7 +2713,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening._default.normal[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.rivalry[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -2723,29 +2723,24 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">rivalry[1]</t>
         </is>
       </c>
       <c r="G93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が{nameA}に向かって叫んだ。「もう我慢の限界よ！ あなたがそうなら、私も本気で行く！」</t>
+          <t xml:space="preserve">因縁の対決！{name1}と{name2}、この大舞台で決着なるか！</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening._default.normal[2]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.rivalry[2]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -2755,29 +2750,24 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening._default.normal[2]</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">rivalry[2]</t>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}の目の色が変わった。「……もういい。あなたがそう思うなら、私も覚悟を決める」</t>
+          <t xml:space="preserve">積み重ねてきた因縁——{name1}と{name2}の物語が、ここで動く！</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening._default.bold[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.tierGap[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -2787,29 +2777,24 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">tierGap[1]</t>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が{nameA}の前に立ちはだかった。「いい加減にして。そのつもりなら、全力で相手になるから」</t>
+          <t xml:space="preserve">{org2}の壁！{name1}は{name2}を越えられるか！</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening._default.bold[2]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.tierGap[2]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -2819,29 +2804,24 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening._default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">tierGap[2]</t>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が{nameA}をまっすぐ見据えた。「もう黙ってられない。受けて立つよ」</t>
+          <t xml:space="preserve">格上挑戦！{name1}が{org2}の{name2}に挑む！</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening._default.quiet[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.closeOVR[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -2851,29 +2831,24 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening._default.quiet[1]</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">closeOVR[1]</t>
         </is>
       </c>
       <c r="G97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が静かに拳を握った。「ずっと信じてた。でももう……終わりにする」</t>
+          <t xml:space="preserve">実力伯仲！{name1}と{name2}、どちらが勝ってもおかしくない！</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening._default.shy[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.closeOVR[2]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -2883,29 +2858,24 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening._default.shy[1]</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">closeOVR[2]</t>
         </is>
       </c>
       <c r="G98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「…ずっと我慢してた…けど…もう限界です…」——{nameB}の声は小さいけど、震えていなかった</t>
+          <t xml:space="preserve">互角の実力——勝敗を分けるのは、この一瞬の判断！</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening._default.shy[2]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.starMatch[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -2915,29 +2885,24 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening._default.shy[2]</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr" s="8">
-        <is>
-          <t xml:space="preserve">内気</t>
+          <t xml:space="preserve">starMatch[1]</t>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が俯いたまま{nameA}に告げた。「…もう…我慢しない…です」</t>
+          <t xml:space="preserve">スター対決！{name1}と{name2}、夢のカードが実現！</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening._default.easygoing[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.starMatch[2]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -2947,29 +2912,24 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening._default.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr" s="9">
-        <is>
-          <t xml:space="preserve">お気楽</t>
+          <t xml:space="preserve">starMatch[2]</t>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}の笑顔が消えた。「……さすがにさ。これはないよ。本気で怒ってるんだからね」</t>
+          <t xml:space="preserve">人気者同士の激突！{name1} vs {name2}、会場が沸く！</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening._default.earnest[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.summit[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -2979,29 +2939,24 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">summit[1]</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が真っ直ぐ{nameA}を見つめた。「ずっと信じていました。でも……もう限界です。本気で行きます」</t>
+          <t xml:space="preserve">団体の威信を懸けた頂上決戦！{name1} vs {name2}！</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening._default.emotional[1]</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES.summit[2]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3011,297 +2966,22 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">summit[2]</t>
         </is>
       </c>
       <c r="G102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が涙を流しながら{nameA}に叫んだ。「なんで……！ なんでそんなことするの……！ もう……もう許さない……！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="40" customHeight="1">
-      <c r="A103" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.rivalry[1]</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">rivalry[1]</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">因縁の対決！{name1}と{name2}、この大舞台で決着なるか！</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="40" customHeight="1">
-      <c r="A104" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.rivalry[2]</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">rivalry[2]</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">積み重ねてきた因縁——{name1}と{name2}の物語が、ここで動く！</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="40" customHeight="1">
-      <c r="A105" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.tierGap[1]</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">tierGap[1]</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{org2}の壁！{name1}は{name2}を越えられるか！</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="40" customHeight="1">
-      <c r="A106" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.tierGap[2]</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">tierGap[2]</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">格上挑戦！{name1}が{org2}の{name2}に挑む！</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="40" customHeight="1">
-      <c r="A107" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.closeOVR[1]</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">closeOVR[1]</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">実力伯仲！{name1}と{name2}、どちらが勝ってもおかしくない！</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="40" customHeight="1">
-      <c r="A108" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.closeOVR[2]</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">closeOVR[2]</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">互角の実力——勝敗を分けるのは、この一瞬の判断！</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="40" customHeight="1">
-      <c r="A109" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.starMatch[1]</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">starMatch[1]</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">スター対決！{name1}と{name2}、夢のカードが実現！</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="40" customHeight="1">
-      <c r="A110" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.starMatch[2]</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">starMatch[2]</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">人気者同士の激突！{name1} vs {name2}、会場が沸く！</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="40" customHeight="1">
-      <c r="A111" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.summit[1]</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">summit[1]</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">団体の威信を懸けた頂上決戦！{name1} vs {name2}！</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="40" customHeight="1">
-      <c r="A112" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES.summit[2]</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">summit[2]</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">年間王者を決める最終決戦——{name1}と{name2}、頂点に立つのはどちらだ！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I112"/>
+  <autoFilter ref="A1:I102"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/ナレーション・記事/実況・演出.xlsx
+++ b/セリフ編集/ナレーション・記事/実況・演出.xlsx
@@ -192,18 +192,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -214,40 +215,45 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">カテゴリ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">出典</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">テーブル</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">パス</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">archetype</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">personality</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">現在</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">改訂</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">備考</t>
         </is>
@@ -261,20 +267,25 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="D2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="12">
+      <c r="E2" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fall[1]</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr" s="3">
+      <c r="H2" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">入ったか…！？ スリーカウントなるかーーーっ！！</t>
         </is>
@@ -288,20 +299,25 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr" s="2">
+      <c r="D3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr" s="12">
+      <c r="E3" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fall[2]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr" s="3">
+      <c r="H3" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">カウントツー！ 返せるのか！？ 返せないのか！？</t>
         </is>
@@ -315,20 +331,25 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
+      <c r="D4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr" s="12">
+      <c r="E4" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fall[3]</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr" s="3">
+      <c r="H4" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">万事休すか…！ {d}、ここが正念場だーっ！</t>
         </is>
@@ -342,20 +363,25 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr" s="2">
+      <c r="D5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr" s="12">
+      <c r="E5" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fall[4]</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr" s="3">
+      <c r="H5" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">このまま決まってしまうのか…！！</t>
         </is>
@@ -369,20 +395,25 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="2">
+      <c r="D6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr" s="12">
+      <c r="E6" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fall[5]</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr" s="3">
+      <c r="H6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">会場が息を飲んでいる…！ {d}の運命やいかにーーっ！</t>
         </is>
@@ -396,20 +427,25 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr" s="2">
+      <c r="D7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr" s="12">
+      <c r="E7" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">gu[1]</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr" s="3">
+      <c r="H7" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">タップするのか…！？ しないのか…！？</t>
         </is>
@@ -423,20 +459,25 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr" s="2">
+      <c r="D8" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr" s="12">
+      <c r="E8" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">gu[2]</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr" s="3">
+      <c r="H8" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ロープに手が届くか…！ {d}、必死に腕を伸ばす…！！</t>
         </is>
@@ -450,20 +491,25 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr" s="2">
+      <c r="D9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr" s="12">
+      <c r="E9" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">gu[3]</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr" s="3">
+      <c r="H9" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{d}の表情が…！ 耐えられるのか！？</t>
         </is>
@@ -477,20 +523,25 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="2">
+      <c r="D10" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr" s="12">
+      <c r="E10" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">gu[4]</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr" s="3">
+      <c r="H10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">レフェリーが確認している…！ ギブアップか…！？</t>
         </is>
@@ -504,20 +555,25 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr" s="2">
+      <c r="D11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr" s="12">
+      <c r="E11" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">gu[5]</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr" s="3">
+      <c r="H11" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">極まっている…！ {d}、絶体絶命だーーっ！</t>
         </is>
@@ -531,20 +587,25 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr" s="2">
+      <c r="D12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr" s="12">
+      <c r="E12" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rollup[1]</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr" s="3">
+      <c r="H12" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">まさかの丸め込み…！ これで決まるのか！？</t>
         </is>
@@ -558,20 +619,25 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr" s="2">
+      <c r="D13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr" s="12">
+      <c r="E13" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">pin[1]</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr" s="3">
+      <c r="H13" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">フォールだ！ 返せるか…！？ カウント…！！</t>
         </is>
@@ -585,20 +651,25 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr" s="2">
+      <c r="D14" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr" s="12">
+      <c r="E14" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">pin[2]</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr" s="3">
+      <c r="H14" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">大技の後のカバー！ {d}、肩を上げられるか…！？</t>
         </is>
@@ -612,20 +683,25 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr" s="2">
+      <c r="D15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr" s="12">
+      <c r="E15" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">pin[3]</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr" s="3">
+      <c r="H15" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ここで勝負を決めに来た！ {d}の運命は…！！</t>
         </is>
@@ -639,20 +715,25 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr" s="2">
+      <c r="D16" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr" s="12">
+      <c r="E16" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">tko[1]</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr" s="3">
+      <c r="H16" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">もう立ち上がれない…！ レフェリーが試合を見ている！</t>
         </is>
@@ -666,20 +747,25 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr" s="2">
+      <c r="D17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr" s="12">
+      <c r="E17" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">tko[2]</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr" s="3">
+      <c r="H17" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">意識が飛んでいる…！ TKOか！？</t>
         </is>
@@ -693,20 +779,25 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">実況・演出</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr" s="2">
+      <c r="D18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">FINISH_SUSPENSE</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr" s="12">
+      <c r="E18" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">tko[3]</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr" s="3">
+      <c r="H18" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">これ以上は危険だ！ ストップがかかるか！？</t>
         </is>
@@ -720,20 +811,25 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr" s="12">
+      <c r="E19" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1]</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr" s="3">
+      <c r="H19" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">二人の連打が止まらない！ これがタッグの醍醐味！</t>
         </is>
@@ -747,20 +843,25 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr" s="12">
+      <c r="E20" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2]</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr" s="3">
+      <c r="H20" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">連携の打撃ラッシュ！ 息がぴったり合っている！</t>
         </is>
@@ -774,20 +875,25 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr" s="12">
+      <c r="E21" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3]</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr" s="3">
+      <c r="H21" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">挟み撃ちの打撃コンビネーション！ 逃げ場がない！</t>
         </is>
@@ -801,20 +907,25 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr" s="12">
+      <c r="E22" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4]</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr" s="3">
+      <c r="H22" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">左右から浴びせる打撃！ 二人の攻撃が完全にシンクロしている！</t>
         </is>
@@ -828,20 +939,25 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr" s="12">
+      <c r="E23" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5]</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr" s="3">
+      <c r="H23" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ダブル打撃の嵐！ 相手は防ぎきれない！</t>
         </is>
@@ -855,20 +971,25 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_STRIKE_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr" s="12">
+      <c r="E24" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[6]</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr" s="3">
+      <c r="H24" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">コンビの拳とキックが次々に突き刺さる！</t>
         </is>
@@ -882,20 +1003,25 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr" s="12">
+      <c r="E25" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1]</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr" s="3">
+      <c r="H25" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">息の合ったダブルスロー！ これぞタッグの真骨頂！</t>
         </is>
@@ -909,20 +1035,25 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr" s="12">
+      <c r="E26" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2]</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr" s="3">
+      <c r="H26" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">二人がかりの豪快な投げ技！ 会場が揺れる！</t>
         </is>
@@ -936,20 +1067,25 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr" s="12">
+      <c r="E27" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3]</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr" s="3">
+      <c r="H27" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">連係の投げ技が完璧に決まった！</t>
         </is>
@@ -963,20 +1099,25 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr" s="12">
+      <c r="E28" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4]</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr" s="3">
+      <c r="H28" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">受け渡し式の投げ技！ 相手は空中で何も出来ない！</t>
         </is>
@@ -990,20 +1131,25 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr" s="12">
+      <c r="E29" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5]</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr" s="3">
+      <c r="H29" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ダブルパワーで投げ切った！ まるで振り子のようだ！</t>
         </is>
@@ -1017,20 +1163,25 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_THROW_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr" s="12">
+      <c r="E30" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[6]</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr" s="3">
+      <c r="H30" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">二人の呼吸が合った一瞬の投げ！ 決まった！</t>
         </is>
@@ -1044,20 +1195,25 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr" s="12">
+      <c r="E31" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1]</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr" s="3">
+      <c r="H31" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">二人がかりの極め技！ もう動けない！</t>
         </is>
@@ -1071,20 +1227,25 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr" s="12">
+      <c r="E32" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2]</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr" s="3">
+      <c r="H32" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">上下から襲いかかる関節技！ これは危険だ！</t>
         </is>
@@ -1098,20 +1259,25 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr" s="12">
+      <c r="E33" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3]</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr" s="3">
+      <c r="H33" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">セットアップから一気に極めた！ 逃げ場がない！</t>
         </is>
@@ -1125,20 +1291,25 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr" s="12">
+      <c r="E34" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4]</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr" s="3">
+      <c r="H34" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ダブルロック！ 二人分の力で関節を締め上げる！</t>
         </is>
@@ -1152,20 +1323,25 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr" s="12">
+      <c r="E35" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5]</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr" s="3">
+      <c r="H35" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">連係の関節技！ 相手は苦悶の表情を浮かべる！</t>
         </is>
@@ -1179,20 +1355,25 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_SUB_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr" s="12">
+      <c r="E36" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[6]</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr" s="3">
+      <c r="H36" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">二人で極めにいった！ これは返せない！</t>
         </is>
@@ -1206,20 +1387,25 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr" s="12">
+      <c r="E37" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1]</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr" s="3">
+      <c r="H37" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">空中から二重の衝撃！ 圧巻のダブルフライ！</t>
         </is>
@@ -1233,20 +1419,25 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr" s="12">
+      <c r="E38" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2]</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr" s="3">
+      <c r="H38" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">タワー式のダイビング技！ 会場が沸いている！</t>
         </is>
@@ -1260,20 +1451,25 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr" s="12">
+      <c r="E39" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3]</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr" s="3">
+      <c r="H39" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">シンクロ空中技が炸裂！ これは止められない！</t>
         </is>
@@ -1287,20 +1483,25 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr" s="12">
+      <c r="E40" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4]</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr" s="3">
+      <c r="H40" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">コンビの飛び技が連続で突き刺さる！</t>
         </is>
@@ -1314,20 +1515,25 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr" s="12">
+      <c r="E41" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5]</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr" s="3">
+      <c r="H41" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">空中戦の完璧な連携！ 二人のタイミングは完全一致！</t>
         </is>
@@ -1341,20 +1547,25 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_AERIAL_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr" s="12">
+      <c r="E42" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[6]</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr" s="3">
+      <c r="H42" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">一人が踏み台、もう一人が飛ぶ！ タッグでしか出来ない技！</t>
         </is>
@@ -1368,20 +1579,25 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr" s="12">
+      <c r="E43" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1]</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr" s="3">
+      <c r="H43" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">これは決まった！ タッグの絆が生んだ一撃！</t>
         </is>
@@ -1395,20 +1611,25 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr" s="12">
+      <c r="E44" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2]</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr" s="3">
+      <c r="H44" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">フィニッシュだ！ 二人の信頼が織りなす必殺技！</t>
         </is>
@@ -1422,20 +1643,25 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr" s="12">
+      <c r="E45" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3]</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr" s="3">
+      <c r="H45" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">息の合った一撃で仕留めた！ これがタッグの勝利！</t>
         </is>
@@ -1449,20 +1675,25 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr" s="12">
+      <c r="E46" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4]</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr" s="3">
+      <c r="H46" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">完璧なダブルチームで決着！ 二人の強さが証明された！</t>
         </is>
@@ -1476,20 +1707,25 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DOUBLE_TEAM_FINISH_COMMENTARY_LINES</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr" s="12">
+      <c r="E47" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5]</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr" s="3">
+      <c r="H47" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">連係の果ての必殺技！ 相手は立てない！</t>
         </is>
@@ -1503,20 +1739,25 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr" s="12">
+      <c r="E48" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1]</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr" s="3">
+      <c r="H48" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{winner}組、見事なコンビネーションで勝利を掴んだ！</t>
         </is>
@@ -1530,20 +1771,25 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr" s="12">
+      <c r="E49" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2]</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr" s="3">
+      <c r="H49" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">息の合ったタッグワークが勝負を決めた！ {winner}&amp;{partner}、完勝！</t>
         </is>
@@ -1557,20 +1803,25 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr" s="12">
+      <c r="E50" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3]</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr" s="3">
+      <c r="H50" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">これがタッグの強さだ！ {winner}組、見事な勝利！</t>
         </is>
@@ -1584,20 +1835,25 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr" s="12">
+      <c r="E51" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4]</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr" s="3">
+      <c r="H51" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{winner}と{partner}の信頼が生んだ一撃！ 歴史に残る名勝負だ！</t>
         </is>
@@ -1611,20 +1867,25 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr" s="12">
+      <c r="E52" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5]</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr" s="3">
+      <c r="H52" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">タッグの醍醐味を見せつけた！ {winner}組、堂々の勝利！</t>
         </is>
@@ -1638,20 +1899,25 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr" s="12">
+      <c r="E53" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[6]</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr" s="3">
+      <c r="H53" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">二人の絆が勝敗を分けた！ {winner}組の勝利！</t>
         </is>
@@ -1665,20 +1931,25 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/tag-battle-lines.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">TAG_MATCH_COMMENTARY_WIN_LINES</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr" s="12">
+      <c r="E54" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[7]</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr" s="3">
+      <c r="H54" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{move}で決着！ {winner}&amp;{partner}のコンビが頂点に立った！</t>
         </is>
@@ -1692,20 +1963,25 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bestFriends[1]</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr" s="3">
+      <c r="H55" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}が練習後に並んで帰る姿が目撃された</t>
         </is>
@@ -1719,20 +1995,25 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bestFriends[2]</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr" s="3">
+      <c r="H56" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}がトレーニングで息の合った動きを見せている</t>
         </is>
@@ -1746,20 +2027,25 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bestFriends[3]</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr" s="3">
+      <c r="H57" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}が{nameB}の体調を気遣っている姿があった</t>
         </is>
@@ -1773,20 +2059,25 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hostileEnemy[1]</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr" s="3">
+      <c r="H58" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}の間に張り詰めた空気が漂っている</t>
         </is>
@@ -1800,20 +2091,25 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hostileEnemy[2]</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr" s="3">
+      <c r="H59" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}が控室で目も合わせない</t>
         </is>
@@ -1827,20 +2123,25 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hostileEnemy[3]</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr" s="3">
+      <c r="H60" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ロッカールームの一角で{nameA}と{nameB}の冷たい空気が流れている</t>
         </is>
@@ -1854,20 +2155,25 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">clash[1]</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr" s="3">
+      <c r="H61" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}が練習中に激しく言い合いになった</t>
         </is>
@@ -1881,20 +2187,25 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">clash[2]</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr" s="3">
+      <c r="H62" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}の口論が控室に響いた</t>
         </is>
@@ -1908,20 +2219,25 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">clash[3]</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr" s="3">
+      <c r="H63" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}が{nameB}に食ってかかり、スタッフが止めに入った</t>
         </is>
@@ -1935,20 +2251,25 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">clash[4]</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr" s="3">
+      <c r="H64" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}の間で一触即発の空気が走った</t>
         </is>
@@ -1962,20 +2283,25 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">clash[5]</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr" s="3">
+      <c r="H65" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}が掴み合いになりかけ、周囲が慌てて止めた</t>
         </is>
@@ -1989,20 +2315,25 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">goodRivalZone[1]</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr" s="3">
+      <c r="H66" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}が{nameB}の試合映像を繰り返し見ている</t>
         </is>
@@ -2016,20 +2347,25 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">goodRivalZone[2]</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr" s="3">
+      <c r="H67" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}が練習後に言葉を交わし、互いに頷いていた</t>
         </is>
@@ -2043,20 +2379,25 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">goodRivalZone[3]</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr" s="3">
+      <c r="H68" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}は{nameB}の試合結果を真っ先に確認している</t>
         </is>
@@ -2070,20 +2411,25 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">unrequitedBond[1]</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr" s="3">
+      <c r="H69" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}が{nameB}に話しかけるも、素っ気ない反応だった</t>
         </is>
@@ -2097,20 +2443,25 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">unrequitedBond[2]</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr" s="3">
+      <c r="H70" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}は{nameB}のことを親友だと思っている——{nameB}がどう思っているかは別として</t>
         </is>
@@ -2124,20 +2475,25 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">unrequitedBond[3]</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr" s="3">
+      <c r="H71" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}が{nameB}を誘うが、{nameB}は別の用事があると去っていった</t>
         </is>
@@ -2151,20 +2507,25 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">onesidedHostility[1]</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr" s="3">
+      <c r="H72" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}が{nameB}を睨みつけている。{nameB}は気づいていない</t>
         </is>
@@ -2178,20 +2539,25 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">onesidedHostility[2]</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr" s="3">
+      <c r="H73" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}は{nameB}の名前を聞くたびに表情を歪めている</t>
         </is>
@@ -2205,20 +2571,25 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">onesidedHostility[3]</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr" s="3">
+      <c r="H74" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}の練習が日に日に荒くなっている——{nameB}への執念が滲む</t>
         </is>
@@ -2232,20 +2603,25 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">temperatureDiff[1]</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr" s="3">
+      <c r="H75" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}が{nameB}との距離に少し戸惑っている様子だ</t>
         </is>
@@ -2259,20 +2635,25 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">temperatureDiff[2]</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr" s="3">
+      <c r="H76" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}は{nameB}との関係をもっと深めたいようだが……</t>
         </is>
@@ -2286,20 +2667,25 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">crossAsymmetry[1]</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr" s="3">
+      <c r="H77" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}は{nameB}を目の敵にしている。{nameB}は{nameA}のことを仲間だと思っているのに</t>
         </is>
@@ -2313,20 +2699,25 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">crossAsymmetry[2]</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr" s="3">
+      <c r="H78" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameB}が笑顔で話しかけた{nameA}は、拳を握りしめて背を向けた</t>
         </is>
@@ -2340,20 +2731,25 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">highRivalryAwareness[1]</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr" s="3">
+      <c r="H79" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}は客席から{nameB}の試合を食い入るように見つめていた</t>
         </is>
@@ -2367,20 +2763,25 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">highRivalryAwareness[2]</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr" s="3">
+      <c r="H80" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}は{nameB}の試合結果を聞いて、ゆっくりとテーピングを巻き直した</t>
         </is>
@@ -2394,20 +2795,25 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">highRivalryAwareness[3]</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr" s="3">
+      <c r="H81" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}が{nameB}の勝利を知り、静かに拳を握った</t>
         </is>
@@ -2421,20 +2827,25 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">highRivalryAwareness[4]</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr" s="3">
+      <c r="H82" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">花道の奥から{nameA}が{nameB}の試合を見ていた。その目は揺れていない</t>
         </is>
@@ -2448,20 +2859,25 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">goodRivalTicker[1]</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr" s="3">
+      <c r="H83" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}が練習後に静かに言葉を交わしていた</t>
         </is>
@@ -2475,20 +2891,25 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">goodRivalTicker[2]</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr" s="3">
+      <c r="H84" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}——好敵手の二人が並んでストレッチをしている</t>
         </is>
@@ -2502,20 +2923,25 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">goodRivalTicker[3]</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr" s="3">
+      <c r="H85" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}は{nameB}の試合を見て、小さく微笑んだ</t>
         </is>
@@ -2529,20 +2955,25 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bitterRivalTicker[1]</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr" s="3">
+      <c r="H86" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}が控室ですれ違い、空気が凍りついた</t>
         </is>
@@ -2556,20 +2987,25 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bitterRivalTicker[2]</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr" s="3">
+      <c r="H87" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}の表情が一瞬歪んだ——{nameB}の名前を聞いただけで</t>
         </is>
@@ -2583,20 +3019,25 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bitterRivalTicker[3]</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr" s="3">
+      <c r="H88" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{nameA}と{nameB}が同じ廊下を歩くことを、誰もが避けさせている</t>
         </is>
@@ -2610,20 +3051,25 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trustWarning[1]</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr" s="3">
+      <c r="H89" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}の表情が最近曇っている</t>
         </is>
@@ -2637,20 +3083,25 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trustWarning[2]</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr" s="3">
+      <c r="H90" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}の練習への集中力が落ちてきている</t>
         </is>
@@ -2664,20 +3115,25 @@
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trustWarning[3]</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr" s="3">
+      <c r="H91" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}がひとりでロッカールームに佇んでいた</t>
         </is>
@@ -2691,20 +3147,25 @@
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr" s="12">
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trustWarning[4]</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr" s="3">
+      <c r="H92" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}の笑顔が減った——周囲もそれに気づいている</t>
         </is>
@@ -2718,20 +3179,25 @@
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr" s="12">
+      <c r="E93" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rivalry[1]</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr" s="3">
+      <c r="H93" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">因縁の対決！{name1}と{name2}、この大舞台で決着なるか！</t>
         </is>
@@ -2745,20 +3211,25 @@
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr" s="12">
+      <c r="E94" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rivalry[2]</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr" s="3">
+      <c r="H94" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">積み重ねてきた因縁——{name1}と{name2}の物語が、ここで動く！</t>
         </is>
@@ -2772,20 +3243,25 @@
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr" s="12">
+      <c r="E95" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">tierGap[1]</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr" s="3">
+      <c r="H95" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{org2}の壁！{name1}は{name2}を越えられるか！</t>
         </is>
@@ -2799,20 +3275,25 @@
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr" s="12">
+      <c r="E96" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">tierGap[2]</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr" s="3">
+      <c r="H96" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">格上挑戦！{name1}が{org2}の{name2}に挑む！</t>
         </is>
@@ -2826,20 +3307,25 @@
       </c>
       <c r="B97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr" s="12">
+      <c r="E97" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">closeOVR[1]</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr" s="3">
+      <c r="H97" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">実力伯仲！{name1}と{name2}、どちらが勝ってもおかしくない！</t>
         </is>
@@ -2853,20 +3339,25 @@
       </c>
       <c r="B98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr" s="12">
+      <c r="E98" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">closeOVR[2]</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr" s="3">
+      <c r="H98" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">互角の実力——勝敗を分けるのは、この一瞬の判断！</t>
         </is>
@@ -2880,20 +3371,25 @@
       </c>
       <c r="B99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr" s="12">
+      <c r="E99" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">starMatch[1]</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr" s="3">
+      <c r="H99" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">スター対決！{name1}と{name2}、夢のカードが実現！</t>
         </is>
@@ -2907,20 +3403,25 @@
       </c>
       <c r="B100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr" s="12">
+      <c r="E100" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">starMatch[2]</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr" s="3">
+      <c r="H100" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">人気者同士の激突！{name1} vs {name2}、会場が沸く！</t>
         </is>
@@ -2934,20 +3435,25 @@
       </c>
       <c r="B101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr" s="12">
+      <c r="E101" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">summit[1]</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr" s="3">
+      <c r="H101" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">団体の威信を懸けた頂上決戦！{name1} vs {name2}！</t>
         </is>
@@ -2961,27 +3467,32 @@
       </c>
       <c r="B102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">実況・演出</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">PPV_HYPE_TEMPLATES</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr" s="12">
+      <c r="E102" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">summit[2]</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr" s="3">
+      <c r="H102" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">年間王者を決める最終決戦——{name1}と{name2}、頂点に立つのはどちらだ！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I102"/>
+  <autoFilter ref="A1:J102"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
